--- a/quizzes/sculpture-19e-niveau2.xlsx
+++ b/quizzes/sculpture-19e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6590719A-449C-476A-B940-203B7F100F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FD3FE2-3CE2-4D3F-A01B-8D1D38102115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="277">
   <si>
     <t>image</t>
   </si>
@@ -62,18 +62,12 @@
     <t>Le Penseur</t>
   </si>
   <si>
-    <t>Antonio Canova</t>
-  </si>
-  <si>
     <t>1793</t>
   </si>
   <si>
     <t>Musée du Louvre, Paris</t>
   </si>
   <si>
-    <t>Psyché ranimée par le baiser de l'Amour</t>
-  </si>
-  <si>
     <t>Bertel Thorvaldsen</t>
   </si>
   <si>
@@ -161,18 +155,6 @@
     <t>Monument à Robert Gould Shaw et au 54e régiment du Massachusetts</t>
   </si>
   <si>
-    <t>Daniel Chester French</t>
-  </si>
-  <si>
-    <t>1911-1920</t>
-  </si>
-  <si>
-    <t>Lincoln Memorial, Washington</t>
-  </si>
-  <si>
-    <t>Abraham Lincoln (Lincoln Memorial)</t>
-  </si>
-  <si>
     <t>David d'Angers</t>
   </si>
   <si>
@@ -206,18 +188,6 @@
     <t>Éros (fontaine commémorative Shaftesbury)</t>
   </si>
   <si>
-    <t>Gustav Vigeland</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>Parc Vigeland, Oslo</t>
-  </si>
-  <si>
-    <t>Le Petit Garçon en colère (Sinnataggen)</t>
-  </si>
-  <si>
     <t>Josef Václav Myslbek</t>
   </si>
   <si>
@@ -383,15 +353,6 @@
     <t>Samuel Adams</t>
   </si>
   <si>
-    <t>Adolf Brütt</t>
-  </si>
-  <si>
-    <t>Aschberg, Naturpark Hüttener Berge, Ascheffel</t>
-  </si>
-  <si>
-    <t>Monument à Bismarck</t>
-  </si>
-  <si>
     <t>Adolf von Hildebrand</t>
   </si>
   <si>
@@ -404,18 +365,6 @@
     <t>Fontaine Wittelsbach (Wittelsbacherbrunnen)</t>
   </si>
   <si>
-    <t>Agustín Querol</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>Glorieta de Quevedo, Madrid</t>
-  </si>
-  <si>
-    <t>Monument à Quevedo</t>
-  </si>
-  <si>
     <t>Albert-Ernest Carrier-Belleuse</t>
   </si>
   <si>
@@ -536,12 +485,6 @@
     <t>Zenobia enchaînée</t>
   </si>
   <si>
-    <t>Jean-Antoine Injalbert</t>
-  </si>
-  <si>
-    <t>1900</t>
-  </si>
-  <si>
     <t>José Piquer y Duart</t>
   </si>
   <si>
@@ -566,39 +509,6 @@
     <t>Tlahuicole</t>
   </si>
   <si>
-    <t>Mariano Benlliure</t>
-  </si>
-  <si>
-    <t>1904-1922</t>
-  </si>
-  <si>
-    <t>Parque del Retiro, Madrid</t>
-  </si>
-  <si>
-    <t>Statue équestre d'Alphonse XII (Monumento a Alfonso XII)</t>
-  </si>
-  <si>
-    <t>Max Klinger</t>
-  </si>
-  <si>
-    <t>Musée des Beaux-Arts, Leipzig</t>
-  </si>
-  <si>
-    <t>Beethoven</t>
-  </si>
-  <si>
-    <t>Medardo Rosso</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>Museo del Novecento, Milan</t>
-  </si>
-  <si>
-    <t>Ecce Puer</t>
-  </si>
-  <si>
     <t>Paul Dubois</t>
   </si>
   <si>
@@ -662,18 +572,6 @@
     <t>Statue de Saigō Takamori</t>
   </si>
   <si>
-    <t>Thomas Brock</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>Devant Buckingham Palace, Londres</t>
-  </si>
-  <si>
-    <t>Monument à la reine Victoria</t>
-  </si>
-  <si>
     <t>Vincenzo Gemito</t>
   </si>
   <si>
@@ -707,9 +605,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8f/Gloria_Victis_-_Anthonin_Merci%C3%A9.jpg/960px-Gloria_Victis_-_Anthonin_Merci%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ef/0_Psych%C3%A9_ranim%C3%A9e_par_le_baiser_de_l%27Amour_-_Canova_-_Louvre_1.JPG/1280px-0_Psych%C3%A9_ranim%C3%A9e_par_le_baiser_de_l%27Amour_-_Canova_-_Louvre_1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f3/Statue-de-la-liberte-new-york.jpg/960px-Statue-de-la-liberte-new-york.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -731,9 +626,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg/960px-La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Lincoln_Memorial_statue_by_Daniel_Chester_French%2C_Washington%2C_D.C_LCCN2011630574.tif/lossy-page1-1280px-Lincoln_Memorial_statue_by_Daniel_Chester_French%2C_Washington%2C_D.C_LCCN2011630574.tif.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/Fronton_Panth%C3%A9on_Paris_1_reframed.jpg/1280px-Fronton_Panth%C3%A9on_Paris_1_reframed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -749,9 +641,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/b/b7/The_Broncho_Buster_MET_1986.81.2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5f/Gustav_Vigeland%2C_ponte%2C_statue_del_1925-33%2C_sinnataggen_%28bambino_arrabbiato%29%2C_ante_1928%2C_02.jpg/1280px-Gustav_Vigeland%2C_ponte%2C_statue_del_1925-33%2C_sinnataggen_%28bambino_arrabbiato%29%2C_ante_1928%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG/960px-The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -800,15 +689,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/58/Berlin_Friedrich_II_Denkmal_09-2017_img1.jpg/960px-Berlin_Friedrich_II_Denkmal_09-2017_img1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/43/Bismarck-Statue_Aschberg_%281%29.jpg/960px-Bismarck-Statue_Aschberg_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/f/f5/Fountain_On_Lenbachplatz_-_panoramio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=de</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9c/Monumento_a_Quevedo_%28Madrid%29_06b.jpg/960px-Monumento_a_Quevedo_%28Madrid%29_06b.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg/960px-Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -836,30 +719,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/49/Hosmer_-_Zenobia_in_Chains_-_front_view_-_HLAMBG.png/330px-Hosmer_-_Zenobia_in_Chains_-_front_view_-_HLAMBG.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/b/b3/P1080006_Paris_XV_et_XVI_pont_Mirabeau_rwk.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
-    <t>La Ville de Paris, La Navigation, Le Commerce et L'Abondance, statues en bronze ornant les piles du pont Mirabeau à Paris[</t>
-  </si>
-  <si>
-    <t>Pont Mirabeau, Paris</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/82/Estatua_de_Miguel_de_Cervantes_%286_de_diciembre_de_2005%2C_Madrid%29_02.JPG/960px-Estatua_de_Miguel_de_Cervantes_%286_de_diciembre_de_2005%2C_Madrid%29_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Museo_Nacional_de_Arte_Mexico_DF%2C_Manuel_Vilarm_Tlahuicole_General_Tlaxcalteca_1851_%2822153403811%29.jpg/960px-Museo_Nacional_de_Arte_Mexico_DF%2C_Manuel_Vilarm_Tlahuicole_General_Tlaxcalteca_1851_%2822153403811%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e4/Monumento_Alfonso_XII%2C_parque_del_Retiro.JPG/1280px-Monumento_Alfonso_XII%2C_parque_del_Retiro.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/58/Leipzig%2C_Museum_der_bildenden_K%C3%BCnste%2C_Max_Klinger%2C_Beethovenskulptur.JPG/960px-Leipzig%2C_Museum_der_bildenden_K%C3%BCnste%2C_Max_Klinger%2C_Beethovenskulptur.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/Medardo_rosso%2C_ecce_puer%2C_1918-20.jpg/960px-Medardo_rosso%2C_ecce_puer%2C_1918-20.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b1/Paul_Dubois_Chanteur_florentin.jpg/960px-Paul_Dubois_Chanteur_florentin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -878,13 +743,127 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/Statue_SaigoTakamori.JPG/960px-Statue_SaigoTakamori.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ad/%22The_Victoria_Memorial%22_London_%22Christmas_day%22_%2815925642490%29.jpg/960px-%22The_Victoria_Memorial%22_London_%22Christmas_day%22_%2815925642490%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/9/94/The_Fisher_Boy_by_Vincenzo_Gemito%2C_Museo_del_Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/06/Cleopatra_by_William_Wetmore_Story_01.jpg/1280px-Cleopatra_by_William_Wetmore_Story_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Edgard Degas</t>
+  </si>
+  <si>
+    <t>Jean-Baptiste Clésinger</t>
+  </si>
+  <si>
+    <t>Louis-Ernest Barrias</t>
+  </si>
+  <si>
+    <t>Henri Chapu</t>
+  </si>
+  <si>
+    <t>Giovanni Dupré</t>
+  </si>
+  <si>
+    <t>Aimé Millet</t>
+  </si>
+  <si>
+    <t>Alfred Boucher</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/a7/Pythia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Pythie</t>
+  </si>
+  <si>
+    <t>Opéra de Paris</t>
+  </si>
+  <si>
+    <t>Adèle d'Affry (pseudo Marcello)</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/ee/Edgar_degas%2C_little_dancer_aged_14%2C_1879-81.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>1878-1881</t>
+  </si>
+  <si>
+    <t>La Petite Danseuse de quatorze ans (1er modèle en cire)</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Sculpture-7808948_%2852096525415%29.jpg/1280px-Sculpture-7808948_%2852096525415%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>La Femme piquée par un serpent</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ad/Alise-Sainte-Reine_-_Statue_de_Vercing%C3%A9torix_-_01.jpg/960px-Alise-Sainte-Reine_-_Statue_de_Vercing%C3%A9torix_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Statue de Vercingétorix</t>
+  </si>
+  <si>
+    <t>Alise-Sainte-Reine, site d'Alésia</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Au_But_%28Alfred_Boucher%29_01.jpg/1280px-Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Au_But_%28Alfred_Boucher%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>Musée Faure, Aix-les-Bains</t>
+  </si>
+  <si>
+    <t>Au but</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/03/Giovanni_dupr%C3%A9%2C_abele_morente_01.jpg/1280px-Giovanni_dupr%C3%A9%2C_abele_morente_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Abel mourant</t>
+  </si>
+  <si>
+    <t>Palazzo Pitti</t>
+  </si>
+  <si>
+    <t>1844-1951</t>
+  </si>
+  <si>
+    <t>La Jeunesse</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d5/La_Jeunesse%2C_S3494%2801%29.jpg/960px-La_Jeunesse%2C_S3494%2801%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Musée Carnavalet, Paris</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/Barrias_La_Nature_se_d%C3%A9voilant.jpg/1920px-Barrias_La_Nature_se_d%C3%A9voilant.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>La Nature se dévoilant à la Science</t>
+  </si>
+  <si>
+    <t>Gustave Crauk</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/55/Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg/960px-Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Statue de Gaspard de Coligny</t>
+  </si>
+  <si>
+    <t>Temple de l’Oratoire du Louvre, Paris</t>
+  </si>
+  <si>
+    <t>Charles Cordier</t>
+  </si>
+  <si>
+    <t>Homme du Soudan</t>
+  </si>
+  <si>
+    <t>1856-1857</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0b/Negre_du_Sudan_Charles_Cordier_Mus%C3%A9e_d%27Orsay.JPG/960px-Negre_du_Sudan_Charles_Cordier_Mus%C3%A9e_d%27Orsay.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -932,12 +911,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -970,18 +950,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1285,13 +1272,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="65.28515625" style="8" customWidth="1"/>
-    <col min="2" max="3" width="22.85546875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="43.5703125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="54" style="8" customWidth="1"/>
+    <col min="1" max="1" width="75" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="43.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="77.7109375" style="3" customWidth="1"/>
+    <col min="6" max="51" width="9.140625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24.95" customHeight="1">
@@ -1312,212 +1301,212 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2" s="10">
+        <v>1870</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C4" s="10">
+        <v>1865</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+      <c r="B7" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1886</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+      <c r="E7" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>115</v>
+      <c r="A8" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>26</v>
+      <c r="A9" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C12" s="7">
+      <c r="A12" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="8">
         <v>1886</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>253</v>
+      <c r="D12" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>136</v>
+      <c r="A13" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>5</v>
@@ -1533,802 +1522,938 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="E15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="A16" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>140</v>
+      <c r="A18" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>144</v>
+      <c r="A19" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>148</v>
+      <c r="A20" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>45</v>
+      <c r="A21" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="4" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>91</v>
+      <c r="A23" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C32" s="8">
+        <v>1869</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="33" spans="1:49">
+      <c r="A33" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:49">
+      <c r="A34" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="35" spans="1:49">
+      <c r="A35" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C35" s="10">
+        <v>1875</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:49">
+      <c r="A36" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:49">
+      <c r="A37" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:49">
+      <c r="A38" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:49" s="6" customFormat="1">
+      <c r="A39" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C39" s="9">
+        <v>1847</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="11"/>
+      <c r="T39" s="11"/>
+      <c r="U39" s="11"/>
+      <c r="V39" s="11"/>
+      <c r="W39" s="11"/>
+      <c r="X39" s="11"/>
+      <c r="Y39" s="11"/>
+      <c r="Z39" s="11"/>
+      <c r="AA39" s="11"/>
+      <c r="AB39" s="11"/>
+      <c r="AC39" s="11"/>
+      <c r="AD39" s="11"/>
+      <c r="AE39" s="11"/>
+      <c r="AF39" s="11"/>
+      <c r="AG39" s="11"/>
+      <c r="AH39" s="11"/>
+      <c r="AI39" s="11"/>
+      <c r="AJ39" s="11"/>
+      <c r="AK39" s="11"/>
+      <c r="AL39" s="11"/>
+      <c r="AM39" s="11"/>
+      <c r="AN39" s="11"/>
+      <c r="AO39" s="11"/>
+      <c r="AP39" s="11"/>
+      <c r="AQ39" s="11"/>
+      <c r="AR39" s="11"/>
+      <c r="AS39" s="11"/>
+      <c r="AT39" s="11"/>
+      <c r="AU39" s="11"/>
+      <c r="AV39" s="11"/>
+      <c r="AW39" s="11"/>
+    </row>
+    <row r="40" spans="1:49">
+      <c r="A40" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:49">
+      <c r="A41" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:49">
+      <c r="A42" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:49">
+      <c r="A43" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:49">
+      <c r="A44" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" spans="1:49">
+      <c r="A45" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:49">
+      <c r="A46" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:49">
+      <c r="A47" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:49">
+      <c r="A48" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C48" s="7">
+        <v>1899</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="49" spans="1:51" s="6" customFormat="1">
+      <c r="A49" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="11"/>
+      <c r="P49" s="11"/>
+      <c r="Q49" s="11"/>
+      <c r="R49" s="11"/>
+      <c r="S49" s="11"/>
+      <c r="T49" s="11"/>
+      <c r="U49" s="11"/>
+      <c r="V49" s="11"/>
+      <c r="W49" s="11"/>
+      <c r="X49" s="11"/>
+      <c r="Y49" s="11"/>
+      <c r="Z49" s="11"/>
+      <c r="AA49" s="11"/>
+      <c r="AB49" s="11"/>
+      <c r="AC49" s="11"/>
+      <c r="AD49" s="11"/>
+      <c r="AE49" s="11"/>
+      <c r="AF49" s="11"/>
+      <c r="AG49" s="11"/>
+      <c r="AH49" s="11"/>
+      <c r="AI49" s="11"/>
+      <c r="AJ49" s="11"/>
+      <c r="AK49" s="11"/>
+      <c r="AL49" s="11"/>
+      <c r="AM49" s="11"/>
+      <c r="AN49" s="11"/>
+      <c r="AO49" s="11"/>
+      <c r="AP49" s="11"/>
+      <c r="AQ49" s="11"/>
+      <c r="AR49" s="11"/>
+      <c r="AS49" s="11"/>
+      <c r="AT49" s="11"/>
+      <c r="AU49" s="11"/>
+      <c r="AV49" s="11"/>
+      <c r="AW49" s="11"/>
+      <c r="AX49" s="11"/>
+      <c r="AY49" s="11"/>
+    </row>
+    <row r="50" spans="1:51">
+      <c r="A50" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="51" spans="1:51" s="6" customFormat="1">
+      <c r="A51" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="11"/>
+      <c r="O51" s="11"/>
+      <c r="P51" s="11"/>
+      <c r="Q51" s="11"/>
+      <c r="R51" s="11"/>
+      <c r="S51" s="11"/>
+      <c r="T51" s="11"/>
+      <c r="U51" s="11"/>
+      <c r="V51" s="11"/>
+      <c r="W51" s="11"/>
+      <c r="X51" s="11"/>
+      <c r="Y51" s="11"/>
+      <c r="Z51" s="11"/>
+      <c r="AA51" s="11"/>
+      <c r="AB51" s="11"/>
+      <c r="AC51" s="11"/>
+      <c r="AD51" s="11"/>
+      <c r="AE51" s="11"/>
+      <c r="AF51" s="11"/>
+      <c r="AG51" s="11"/>
+      <c r="AH51" s="11"/>
+      <c r="AI51" s="11"/>
+      <c r="AJ51" s="11"/>
+      <c r="AK51" s="11"/>
+      <c r="AL51" s="11"/>
+      <c r="AM51" s="11"/>
+      <c r="AN51" s="11"/>
+      <c r="AO51" s="11"/>
+      <c r="AP51" s="11"/>
+      <c r="AQ51" s="11"/>
+      <c r="AR51" s="11"/>
+      <c r="AS51" s="11"/>
+      <c r="AT51" s="11"/>
+      <c r="AU51" s="11"/>
+      <c r="AV51" s="11"/>
+      <c r="AW51" s="11"/>
+      <c r="AX51" s="11"/>
+      <c r="AY51" s="11"/>
+    </row>
+    <row r="52" spans="1:51">
+      <c r="A52" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="53" spans="1:51">
+      <c r="A53" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:51">
+      <c r="A54" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:51">
+      <c r="A55" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="56" spans="1:51">
+      <c r="A56" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="57" spans="1:51">
+      <c r="A57" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="58" spans="1:51">
+      <c r="A58" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="59" spans="1:51">
+      <c r="A59" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60" spans="1:51">
+      <c r="A60" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="61" spans="1:51">
+      <c r="A61" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B47" s="2" t="s">
+      <c r="B61" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="E61" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -2337,65 +2462,64 @@
   </sortState>
   <hyperlinks>
     <hyperlink ref="A14" r:id="rId1" xr:uid="{09F23F0B-B050-4759-9DB4-F32D47F7729E}"/>
-    <hyperlink ref="A11" r:id="rId2" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ef/0_Psych%C3%A9_ranim%C3%A9e_par_le_baiser_de_l%27Amour_-_Canova_-_Louvre_1.JPG/1280px-0_Psych%C3%A9_ranim%C3%A9e_par_le_baiser_de_l%27Amour_-_Canova_-_Louvre_1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C1F4FE95-8F38-43E2-9C08-D2912A1487EA}"/>
-    <hyperlink ref="A16" r:id="rId3" xr:uid="{167916C4-CEFD-4D99-AD07-8C9696B932B0}"/>
-    <hyperlink ref="A17" r:id="rId4" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg/960px-La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{052CBE40-3C32-4FA7-959E-1E8236934F2F}"/>
-    <hyperlink ref="A36" r:id="rId5" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG/960px-Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AA11E9C2-3F00-4665-BF86-A6AEE9A510FC}"/>
-    <hyperlink ref="A9" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{4491912E-A9C1-4B07-B8CB-CD441BDAD3C9}"/>
-    <hyperlink ref="A26" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD408641-35F1-4B9D-87B3-16646ABDBCE7}"/>
-    <hyperlink ref="A24" r:id="rId8" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg/960px-%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E8F3965E-F5A8-4D2A-AE8F-7950838C5304}"/>
-    <hyperlink ref="A34" r:id="rId9" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg/960px-Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9596A09F-13D1-40A4-B63A-6661CC9F685A}"/>
-    <hyperlink ref="A15" r:id="rId10" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG/1280px-Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{80D8AADC-5887-4FDC-9B85-272CFC4070EE}"/>
-    <hyperlink ref="A21" r:id="rId11" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Lincoln_Memorial_statue_by_Daniel_Chester_French%2C_Washington%2C_D.C_LCCN2011630574.tif/lossy-page1-1280px-Lincoln_Memorial_statue_by_Daniel_Chester_French%2C_Washington%2C_D.C_LCCN2011630574.tif.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A87829FC-DF93-4C96-985F-34EE40363CE9}"/>
-    <hyperlink ref="A22" r:id="rId12" xr:uid="{17D8F98E-B3C5-40EE-96F4-561BD7B71421}"/>
-    <hyperlink ref="A43" r:id="rId13" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/57/Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg/960px-Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AC835F77-4F4D-4E22-9C5B-4EDB9350B5A3}"/>
-    <hyperlink ref="A7" r:id="rId14" xr:uid="{F2505485-83E8-48EA-BB4D-F588B71C58DB}"/>
-    <hyperlink ref="A30" r:id="rId15" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/5f/Gustav_Vigeland%2C_ponte%2C_statue_del_1925-33%2C_sinnataggen_%28bambino_arrabbiato%29%2C_ante_1928%2C_02.jpg/1280px-Gustav_Vigeland%2C_ponte%2C_statue_del_1925-33%2C_sinnataggen_%28bambino_arrabbiato%29%2C_ante_1928%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{59D46A2C-58FA-40FA-8183-29F34CE71A89}"/>
-    <hyperlink ref="A42" r:id="rId16" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/34/%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg/960px-%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43B59558-28D1-4973-9A22-0504AF1AF29D}"/>
-    <hyperlink ref="A33" r:id="rId17" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG/960px-The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E8139FE8-3723-4E5F-BF98-CF01769E1C90}"/>
-    <hyperlink ref="A40" r:id="rId18" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png/960px-John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3C64EB19-6037-401A-96C8-3454405E42C5}"/>
-    <hyperlink ref="A47" r:id="rId19" xr:uid="{6362D38B-2A96-42D3-B165-07B2A2DF56DE}"/>
-    <hyperlink ref="A52" r:id="rId20" xr:uid="{F45C10D3-1765-4C96-8F78-C6EE693E8C45}"/>
-    <hyperlink ref="A53" r:id="rId21" xr:uid="{8A1ECCB2-671E-4488-826E-B358EC04F5FE}"/>
-    <hyperlink ref="A58" r:id="rId22" xr:uid="{A6648C49-C63D-4AC1-A6BC-F29C9BCF54AA}"/>
-    <hyperlink ref="A23" r:id="rId23" xr:uid="{D6E97BAF-4A03-4F7B-B834-6B6D97D667C1}"/>
-    <hyperlink ref="A28" r:id="rId24" xr:uid="{C871F16A-85A8-477B-A877-84B16C4070B2}"/>
-    <hyperlink ref="A44" r:id="rId25" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ed/Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG/1280px-Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B3F96645-4A24-45B5-BCCB-F52FB6D89AD0}"/>
-    <hyperlink ref="A10" r:id="rId26" xr:uid="{2E1B7B52-3CF8-48D8-86EC-74C1511A12E7}"/>
-    <hyperlink ref="A39" r:id="rId27" xr:uid="{B734EAF9-0CAC-48FF-8068-DFD62AF03E54}"/>
-    <hyperlink ref="A37" r:id="rId28" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG/960px-L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E3E5E906-4404-48D4-A232-36BFE32A667D}"/>
-    <hyperlink ref="A38" r:id="rId29" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/75/J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg/1280px-J._Lambeaux%2C_de_menselijke_driften_-_354620_-_onroerenderfgoed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FF7B8E11-B264-4306-8709-62FAB8487E45}"/>
-    <hyperlink ref="A8" r:id="rId30" xr:uid="{CA3BD580-A46F-44BE-9482-9589EA939FAB}"/>
-    <hyperlink ref="A18" r:id="rId31" xr:uid="{E39C5043-03DE-4295-A981-9E958DF63DBF}"/>
-    <hyperlink ref="A2" r:id="rId32" xr:uid="{C35B3D14-AAB8-4964-B8AE-93DD492E0E0E}"/>
-    <hyperlink ref="A3" r:id="rId33" xr:uid="{89BFC874-8B1C-4D17-B994-2B65C747E8C0}"/>
-    <hyperlink ref="A4" r:id="rId34" xr:uid="{D3E768A5-591D-440D-8296-34FC0A710600}"/>
-    <hyperlink ref="A5" r:id="rId35" xr:uid="{2557FBA1-BFB3-48AD-B9DD-1258F5055F5A}"/>
-    <hyperlink ref="A6" r:id="rId36" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Alexandre_Falgui%C3%A8re_-_Vainqueur_au_combat_de_coqs_%281864%29.jpg/1280px-Alexandre_Falgui%C3%A8re_-_Vainqueur_au_combat_de_coqs_%281864%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{66400BC1-750E-4E87-8FBE-FD7F73FC6627}"/>
-    <hyperlink ref="A12" r:id="rId37" xr:uid="{3C778E09-A8CF-4EC5-97F2-9ADBB4AA4B61}"/>
-    <hyperlink ref="A13" r:id="rId38" xr:uid="{9B504E9C-BEFD-44B3-B869-73F9586CB5DD}"/>
-    <hyperlink ref="A19" r:id="rId39" xr:uid="{F96C6218-3DC6-429C-B97C-87BF1E56849A}"/>
-    <hyperlink ref="A20" r:id="rId40" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7d/%D0%92%D0%B0%D1%80%D1%88%D0%B0%D0%B2%D0%B0_-_panoramio_%28130%29.jpg/960px-%D0%92%D0%B0%D1%80%D1%88%D0%B0%D0%B2%D0%B0_-_panoramio_%28130%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C8A305DF-A6C9-495D-A1AE-772305FE8261}"/>
-    <hyperlink ref="A25" r:id="rId41" xr:uid="{2F6A5E41-3E4A-4779-A7AC-6E7CCB64D22F}"/>
-    <hyperlink ref="A27" r:id="rId42" xr:uid="{69ED9E12-C396-431B-B8F1-F28D0A602E98}"/>
-    <hyperlink ref="A29" r:id="rId43" xr:uid="{5D77A0CA-8CD6-4D49-A28D-511CDA7EB67C}"/>
-    <hyperlink ref="A31" r:id="rId44" xr:uid="{514B81EE-8CFE-4D60-B5B0-5356CB9EA31C}"/>
-    <hyperlink ref="A32" r:id="rId45" xr:uid="{23FD7F71-63B7-4AB4-8686-0324907807CC}"/>
-    <hyperlink ref="A35" r:id="rId46" xr:uid="{C77FA828-BEA4-4AA7-B75A-2FA2860A4F18}"/>
-    <hyperlink ref="A41" r:id="rId47" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/82/Estatua_de_Miguel_de_Cervantes_%286_de_diciembre_de_2005%2C_Madrid%29_02.JPG/960px-Estatua_de_Miguel_de_Cervantes_%286_de_diciembre_de_2005%2C_Madrid%29_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3C5133CF-9130-42BB-A7D6-CB138529FEF1}"/>
-    <hyperlink ref="A45" r:id="rId48" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Museo_Nacional_de_Arte_Mexico_DF%2C_Manuel_Vilarm_Tlahuicole_General_Tlaxcalteca_1851_%2822153403811%29.jpg/960px-Museo_Nacional_de_Arte_Mexico_DF%2C_Manuel_Vilarm_Tlahuicole_General_Tlaxcalteca_1851_%2822153403811%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{79E9BD51-D020-4923-B07B-A9E25539D93B}"/>
-    <hyperlink ref="A46" r:id="rId49" xr:uid="{F9D585BA-93D1-4993-BB2C-3CB89ABD89FC}"/>
-    <hyperlink ref="A48" r:id="rId50" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/58/Leipzig%2C_Museum_der_bildenden_K%C3%BCnste%2C_Max_Klinger%2C_Beethovenskulptur.JPG/960px-Leipzig%2C_Museum_der_bildenden_K%C3%BCnste%2C_Max_Klinger%2C_Beethovenskulptur.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EEF06452-BEC3-497D-9C7D-C11AA7948678}"/>
-    <hyperlink ref="A49" r:id="rId51" xr:uid="{DEF544B4-5EC1-47BD-B552-F224FB8DBE9D}"/>
-    <hyperlink ref="A50" r:id="rId52" xr:uid="{A7D3B521-73D8-4D12-859C-2BDA5FC5C9BD}"/>
-    <hyperlink ref="A51" r:id="rId53" xr:uid="{CA64DF7E-88F5-4722-9B9E-3997A75ED0E6}"/>
-    <hyperlink ref="A54" r:id="rId54" xr:uid="{8D8DDFC6-5BF8-4844-8322-7EA28FA6DABB}"/>
-    <hyperlink ref="A55" r:id="rId55" xr:uid="{6064E09D-244B-4911-A11E-B70667B83E98}"/>
-    <hyperlink ref="A56" r:id="rId56" xr:uid="{AAF4E702-D56A-42D5-B8AC-681CCB9FEA8B}"/>
-    <hyperlink ref="A57" r:id="rId57" xr:uid="{4D5F0FFE-B7F1-44B3-AF08-F23CBE027110}"/>
-    <hyperlink ref="A59" r:id="rId58" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/ad/%22The_Victoria_Memorial%22_London_%22Christmas_day%22_%2815925642490%29.jpg/960px-%22The_Victoria_Memorial%22_London_%22Christmas_day%22_%2815925642490%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{84568828-8C92-44E4-994C-9691D67A6EE0}"/>
-    <hyperlink ref="A60" r:id="rId59" xr:uid="{5B30924F-F0D1-4E32-AB4E-55BA8203119E}"/>
-    <hyperlink ref="A61" r:id="rId60" xr:uid="{C3FEF373-80EC-4A05-90A7-AEB83324E5A6}"/>
+    <hyperlink ref="A16" r:id="rId2" xr:uid="{167916C4-CEFD-4D99-AD07-8C9696B932B0}"/>
+    <hyperlink ref="A17" r:id="rId3" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg/960px-La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{052CBE40-3C32-4FA7-959E-1E8236934F2F}"/>
+    <hyperlink ref="A38" r:id="rId4" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG/960px-Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AA11E9C2-3F00-4665-BF86-A6AEE9A510FC}"/>
+    <hyperlink ref="A27" r:id="rId5" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD408641-35F1-4B9D-87B3-16646ABDBCE7}"/>
+    <hyperlink ref="A25" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg/960px-%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E8F3965E-F5A8-4D2A-AE8F-7950838C5304}"/>
+    <hyperlink ref="A37" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg/960px-Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9596A09F-13D1-40A4-B63A-6661CC9F685A}"/>
+    <hyperlink ref="A15" r:id="rId8" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG/1280px-Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{80D8AADC-5887-4FDC-9B85-272CFC4070EE}"/>
+    <hyperlink ref="A22" r:id="rId9" xr:uid="{17D8F98E-B3C5-40EE-96F4-561BD7B71421}"/>
+    <hyperlink ref="A46" r:id="rId10" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/57/Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg/960px-Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AC835F77-4F4D-4E22-9C5B-4EDB9350B5A3}"/>
+    <hyperlink ref="A8" r:id="rId11" xr:uid="{F2505485-83E8-48EA-BB4D-F588B71C58DB}"/>
+    <hyperlink ref="A45" r:id="rId12" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/34/%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg/960px-%D0%9F%D1%80%D0%B0%D0%B3%D0%B0.%D0%9F%D0%B0%D0%BC%D1%8F%D1%82%D0%BD%D0%B8%D0%BA_%D0%92%D0%B0%D1%86%D0%BB%D0%B0%D0%B2%D1%83.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43B59558-28D1-4973-9A22-0504AF1AF29D}"/>
+    <hyperlink ref="A36" r:id="rId13" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG/960px-The_Greek_Slave_by_Hiram_Powers%2C_modeled_1841-1843%2C_carved_1846_-_Corcoran_Gallery_of_Art_-_DSC01077.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E8139FE8-3723-4E5F-BF98-CF01769E1C90}"/>
+    <hyperlink ref="A43" r:id="rId14" display="https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png/960px-John_Gibson_%281790-1866%29_-_The_Tinted_Venus_%281862%29_front%2C_Walker_Art_Gallery%2C_Liverpool%2C_May_2012_%2835185842510%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3C64EB19-6037-401A-96C8-3454405E42C5}"/>
+    <hyperlink ref="A50" r:id="rId15" xr:uid="{6362D38B-2A96-42D3-B165-07B2A2DF56DE}"/>
+    <hyperlink ref="A53" r:id="rId16" xr:uid="{F45C10D3-1765-4C96-8F78-C6EE693E8C45}"/>
+    <hyperlink ref="A54" r:id="rId17" xr:uid="{8A1ECCB2-671E-4488-826E-B358EC04F5FE}"/>
+    <hyperlink ref="A59" r:id="rId18" xr:uid="{A6648C49-C63D-4AC1-A6BC-F29C9BCF54AA}"/>
+    <hyperlink ref="A24" r:id="rId19" xr:uid="{D6E97BAF-4A03-4F7B-B834-6B6D97D667C1}"/>
+    <hyperlink ref="A29" r:id="rId20" xr:uid="{C871F16A-85A8-477B-A877-84B16C4070B2}"/>
+    <hyperlink ref="A47" r:id="rId21" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ed/Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG/1280px-Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B3F96645-4A24-45B5-BCCB-F52FB6D89AD0}"/>
+    <hyperlink ref="A11" r:id="rId22" xr:uid="{2E1B7B52-3CF8-48D8-86EC-74C1511A12E7}"/>
+    <hyperlink ref="A42" r:id="rId23" xr:uid="{B734EAF9-0CAC-48FF-8068-DFD62AF03E54}"/>
+    <hyperlink ref="A40" r:id="rId24" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG/960px-L0393_-_Mus%C3%A9e_d%27Orsay_-_Tanagra_par_Jean_L%C3%A9on_G%C3%A9rome.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E3E5E906-4404-48D4-A232-36BFE32A667D}"/>
+    <hyperlink ref="A9" r:id="rId25" xr:uid="{CA3BD580-A46F-44BE-9482-9589EA939FAB}"/>
+    <hyperlink ref="A19" r:id="rId26" xr:uid="{E39C5043-03DE-4295-A981-9E958DF63DBF}"/>
+    <hyperlink ref="A3" r:id="rId27" xr:uid="{89BFC874-8B1C-4D17-B994-2B65C747E8C0}"/>
+    <hyperlink ref="A6" r:id="rId28" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Alexandre_Falgui%C3%A8re_-_Vainqueur_au_combat_de_coqs_%281864%29.jpg/1280px-Alexandre_Falgui%C3%A8re_-_Vainqueur_au_combat_de_coqs_%281864%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{66400BC1-750E-4E87-8FBE-FD7F73FC6627}"/>
+    <hyperlink ref="A13" r:id="rId29" xr:uid="{9B504E9C-BEFD-44B3-B869-73F9586CB5DD}"/>
+    <hyperlink ref="A20" r:id="rId30" xr:uid="{F96C6218-3DC6-429C-B97C-87BF1E56849A}"/>
+    <hyperlink ref="A21" r:id="rId31" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7d/%D0%92%D0%B0%D1%80%D1%88%D0%B0%D0%B2%D0%B0_-_panoramio_%28130%29.jpg/960px-%D0%92%D0%B0%D1%80%D1%88%D0%B0%D0%B2%D0%B0_-_panoramio_%28130%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C8A305DF-A6C9-495D-A1AE-772305FE8261}"/>
+    <hyperlink ref="A26" r:id="rId32" xr:uid="{2F6A5E41-3E4A-4779-A7AC-6E7CCB64D22F}"/>
+    <hyperlink ref="A28" r:id="rId33" xr:uid="{69ED9E12-C396-431B-B8F1-F28D0A602E98}"/>
+    <hyperlink ref="A31" r:id="rId34" xr:uid="{5D77A0CA-8CD6-4D49-A28D-511CDA7EB67C}"/>
+    <hyperlink ref="A33" r:id="rId35" xr:uid="{514B81EE-8CFE-4D60-B5B0-5356CB9EA31C}"/>
+    <hyperlink ref="A34" r:id="rId36" xr:uid="{23FD7F71-63B7-4AB4-8686-0324907807CC}"/>
+    <hyperlink ref="A44" r:id="rId37" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/82/Estatua_de_Miguel_de_Cervantes_%286_de_diciembre_de_2005%2C_Madrid%29_02.JPG/960px-Estatua_de_Miguel_de_Cervantes_%286_de_diciembre_de_2005%2C_Madrid%29_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3C5133CF-9130-42BB-A7D6-CB138529FEF1}"/>
+    <hyperlink ref="A49" r:id="rId38" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Museo_Nacional_de_Arte_Mexico_DF%2C_Manuel_Vilarm_Tlahuicole_General_Tlaxcalteca_1851_%2822153403811%29.jpg/960px-Museo_Nacional_de_Arte_Mexico_DF%2C_Manuel_Vilarm_Tlahuicole_General_Tlaxcalteca_1851_%2822153403811%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{79E9BD51-D020-4923-B07B-A9E25539D93B}"/>
+    <hyperlink ref="A51" r:id="rId39" xr:uid="{A7D3B521-73D8-4D12-859C-2BDA5FC5C9BD}"/>
+    <hyperlink ref="A52" r:id="rId40" xr:uid="{CA64DF7E-88F5-4722-9B9E-3997A75ED0E6}"/>
+    <hyperlink ref="A55" r:id="rId41" xr:uid="{8D8DDFC6-5BF8-4844-8322-7EA28FA6DABB}"/>
+    <hyperlink ref="A56" r:id="rId42" xr:uid="{6064E09D-244B-4911-A11E-B70667B83E98}"/>
+    <hyperlink ref="A57" r:id="rId43" xr:uid="{AAF4E702-D56A-42D5-B8AC-681CCB9FEA8B}"/>
+    <hyperlink ref="A58" r:id="rId44" xr:uid="{4D5F0FFE-B7F1-44B3-AF08-F23CBE027110}"/>
+    <hyperlink ref="A60" r:id="rId45" xr:uid="{5B30924F-F0D1-4E32-AB4E-55BA8203119E}"/>
+    <hyperlink ref="A61" r:id="rId46" xr:uid="{C3FEF373-80EC-4A05-90A7-AEB83324E5A6}"/>
+    <hyperlink ref="A5" r:id="rId47" xr:uid="{A48CCD89-6B56-4EFB-8B6C-0A0ECFB8F8D9}"/>
+    <hyperlink ref="A10" r:id="rId48" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{E0F148C3-98D3-4E2A-8358-EC141CC2F650}"/>
+    <hyperlink ref="A12" r:id="rId49" xr:uid="{FDCF47B0-83FC-43BA-AB5E-5BC09158CB1B}"/>
+    <hyperlink ref="A2" r:id="rId50" xr:uid="{D9C63A8D-77EF-4A24-B9AE-8F969F98DF09}"/>
+    <hyperlink ref="A23" r:id="rId51" xr:uid="{71A67ADA-0476-4DFA-936A-C01BA1530CFD}"/>
+    <hyperlink ref="A39" r:id="rId52" xr:uid="{AE678BD0-0675-4E63-AE8B-3C4F5ECC09A8}"/>
+    <hyperlink ref="A4" r:id="rId53" xr:uid="{2A739E13-8E3D-4F75-98E1-B2F4CF151CE6}"/>
+    <hyperlink ref="A7" r:id="rId54" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Au_But_%28Alfred_Boucher%29_01.jpg/1280px-Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Au_But_%28Alfred_Boucher%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{C2C06555-D109-465D-866A-4425B3188ADF}"/>
+    <hyperlink ref="A30" r:id="rId55" xr:uid="{B4AB73FA-E9A5-492E-8460-0035A08F308A}"/>
+    <hyperlink ref="A35" r:id="rId56" xr:uid="{F973385B-28E1-4561-B45F-9E74717E7F46}"/>
+    <hyperlink ref="A48" r:id="rId57" xr:uid="{25939432-0835-4ADE-B2CC-A35A5B80D956}"/>
+    <hyperlink ref="A32" r:id="rId58" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/55/Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg/960px-Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2F91C6EB-DC08-4036-AA37-7146C9AE0D12}"/>
+    <hyperlink ref="A18" r:id="rId59" xr:uid="{28AA9905-A101-4E4D-B41B-763B78D611CD}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-19e-niveau2.xlsx
+++ b/quizzes/sculpture-19e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FD3FE2-3CE2-4D3F-A01B-8D1D38102115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD650EF9-1A7B-411B-9EEE-0895E2573F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="277">
   <si>
     <t>image</t>
   </si>
@@ -455,15 +455,6 @@
     <t>Athlète luttant avec un python</t>
   </si>
   <si>
-    <t>Giovanni Duprè</t>
-  </si>
-  <si>
-    <t>Musée de l'Ermitage, Saint-Pétersbourg (original) / Galerie d'art moderne, Palazzo Pitti, Florence (bronze)</t>
-  </si>
-  <si>
-    <t>Abele morente (Abel mourant)</t>
-  </si>
-  <si>
     <t>Hamo Thornycroft</t>
   </si>
   <si>
@@ -710,9 +701,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/An_athlete_wrestling_a_python.png/960px-An_athlete_wrestling_a_python.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Dupre_abel_morente_4.jpg/1280px-Dupre_abel_morente_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Hamo_Thornycroft-Teucer-07211.jpg/960px-Hamo_Thornycroft-Teucer-07211.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -864,6 +852,18 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0b/Negre_du_Sudan_Charles_Cordier_Mus%C3%A9e_d%27Orsay.JPG/960px-Negre_du_Sudan_Charles_Cordier_Mus%C3%A9e_d%27Orsay.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f6/Belgique_-_Bruxelles_-_Botanique_-_L%27Automne_ou_Le_Semeur_de_Constantin_Meunier_-_01.jpg/960px-Belgique_-_Bruxelles_-_Botanique_-_L%27Automne_ou_Le_Semeur_de_Constantin_Meunier_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Le_Masque-Ernest_Christophe-IMG_8124-black.jpg/1920px-Le_Masque-Ernest_Christophe-IMG_8124-black.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Ernest Christophe</t>
+  </si>
+  <si>
+    <t>La Comédie humaine (dit aussi Le Masque) </t>
   </si>
 </sst>
 </file>
@@ -1302,24 +1302,24 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C2" s="10">
         <v>1870</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>106</v>
@@ -1336,24 +1336,24 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C4" s="10">
         <v>1865</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>110</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>113</v>
@@ -1387,24 +1387,24 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C7" s="10">
         <v>1886</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>48</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>103</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>22</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>89</v>
@@ -1472,24 +1472,24 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C12" s="8">
         <v>1886</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>116</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>5</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>36</v>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>11</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>15</v>
@@ -1574,24 +1574,24 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>120</v>
@@ -1608,7 +1608,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
-        <v>221</v>
+        <v>273</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>124</v>
@@ -1625,7 +1625,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>128</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>40</v>
@@ -1659,24 +1659,24 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>79</v>
@@ -1693,7 +1693,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>29</v>
@@ -1710,177 +1710,177 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>223</v>
+        <v>274</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>133</v>
+        <v>275</v>
+      </c>
+      <c r="C26" s="5">
+        <v>1876</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>135</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>26</v>
+        <v>133</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="4" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>137</v>
+        <v>26</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>139</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>261</v>
+        <v>198</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>142</v>
+        <v>256</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C32" s="8">
         <v>1869</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" spans="1:49">
       <c r="A33" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>138</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:49">
       <c r="A34" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:49">
       <c r="A35" s="4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C35" s="10">
         <v>1875</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="36" spans="1:49">
       <c r="A36" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>55</v>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="37" spans="1:49">
       <c r="A37" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>33</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="38" spans="1:49">
       <c r="A38" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>18</v>
@@ -1931,10 +1931,10 @@
     </row>
     <row r="39" spans="1:49" s="6" customFormat="1">
       <c r="A39" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C39" s="9">
         <v>1847</v>
@@ -1943,7 +1943,7 @@
         <v>20</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F39" s="11"/>
       <c r="G39" s="11"/>
@@ -1992,7 +1992,7 @@
     </row>
     <row r="40" spans="1:49">
       <c r="A40" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>96</v>
@@ -2009,7 +2009,7 @@
     </row>
     <row r="41" spans="1:49">
       <c r="A41" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>99</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="42" spans="1:49">
       <c r="A42" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>93</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="43" spans="1:49">
       <c r="A43" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>59</v>
@@ -2060,24 +2060,24 @@
     </row>
     <row r="44" spans="1:49">
       <c r="A44" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="45" spans="1:49">
       <c r="A45" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>51</v>
@@ -2094,7 +2094,7 @@
     </row>
     <row r="46" spans="1:49">
       <c r="A46" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>44</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="47" spans="1:49">
       <c r="A47" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>86</v>
@@ -2128,10 +2128,10 @@
     </row>
     <row r="48" spans="1:49">
       <c r="A48" s="4" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C48" s="7">
         <v>1899</v>
@@ -2140,24 +2140,24 @@
         <v>20</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49" spans="1:51" s="6" customFormat="1">
       <c r="A49" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E49" s="5" t="s">
         <v>154</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>157</v>
       </c>
       <c r="F49" s="11"/>
       <c r="G49" s="11"/>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="50" spans="1:51">
       <c r="A50" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>63</v>
@@ -2225,19 +2225,19 @@
     </row>
     <row r="51" spans="1:51" s="6" customFormat="1">
       <c r="A51" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F51" s="11"/>
       <c r="G51" s="11"/>
@@ -2288,24 +2288,24 @@
     </row>
     <row r="52" spans="1:51">
       <c r="A52" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C52" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D52" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>162</v>
-      </c>
       <c r="E52" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="53" spans="1:51">
       <c r="A53" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>67</v>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="54" spans="1:51">
       <c r="A54" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>71</v>
@@ -2339,75 +2339,75 @@
     </row>
     <row r="55" spans="1:51">
       <c r="A55" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B55" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:51">
       <c r="A56" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:51">
       <c r="A57" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B57" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>171</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:51">
       <c r="A58" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B58" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="59" spans="1:51">
       <c r="A59" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>75</v>
@@ -2424,36 +2424,36 @@
     </row>
     <row r="60" spans="1:51">
       <c r="A60" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B60" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>179</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="61" spans="1:51">
       <c r="A61" s="4" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>73</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2465,7 +2465,7 @@
     <hyperlink ref="A16" r:id="rId2" xr:uid="{167916C4-CEFD-4D99-AD07-8C9696B932B0}"/>
     <hyperlink ref="A17" r:id="rId3" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg/960px-La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{052CBE40-3C32-4FA7-959E-1E8236934F2F}"/>
     <hyperlink ref="A38" r:id="rId4" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG/960px-Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AA11E9C2-3F00-4665-BF86-A6AEE9A510FC}"/>
-    <hyperlink ref="A27" r:id="rId5" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD408641-35F1-4B9D-87B3-16646ABDBCE7}"/>
+    <hyperlink ref="A28" r:id="rId5" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD408641-35F1-4B9D-87B3-16646ABDBCE7}"/>
     <hyperlink ref="A25" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg/960px-%22Gorille_enlevant_une_femme%22_%28Palais_de_Tokyo%29_%287670344022%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E8F3965E-F5A8-4D2A-AE8F-7950838C5304}"/>
     <hyperlink ref="A37" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg/960px-Sapho_de_James_Pradier_%281852%29%2C_Mus%C3%A9e_d%27Orsay.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9596A09F-13D1-40A4-B63A-6661CC9F685A}"/>
     <hyperlink ref="A15" r:id="rId8" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG/1280px-Memorial_to_Robert_Gould_Shaw_and_the_54th_Massachusetts_Volunteer_Infantry_Regiment%2C_Boston.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{80D8AADC-5887-4FDC-9B85-272CFC4070EE}"/>
@@ -2480,7 +2480,7 @@
     <hyperlink ref="A54" r:id="rId17" xr:uid="{8A1ECCB2-671E-4488-826E-B358EC04F5FE}"/>
     <hyperlink ref="A59" r:id="rId18" xr:uid="{A6648C49-C63D-4AC1-A6BC-F29C9BCF54AA}"/>
     <hyperlink ref="A24" r:id="rId19" xr:uid="{D6E97BAF-4A03-4F7B-B834-6B6D97D667C1}"/>
-    <hyperlink ref="A29" r:id="rId20" xr:uid="{C871F16A-85A8-477B-A877-84B16C4070B2}"/>
+    <hyperlink ref="A30" r:id="rId20" xr:uid="{C871F16A-85A8-477B-A877-84B16C4070B2}"/>
     <hyperlink ref="A47" r:id="rId21" display="https://upload.wikimedia.org/wikipedia/commons/thumb/e/ed/Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG/1280px-Lorenzo_bartolini%2C_ninfa_dello_scorpione%2C_1845%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B3F96645-4A24-45B5-BCCB-F52FB6D89AD0}"/>
     <hyperlink ref="A11" r:id="rId22" xr:uid="{2E1B7B52-3CF8-48D8-86EC-74C1511A12E7}"/>
     <hyperlink ref="A42" r:id="rId23" xr:uid="{B734EAF9-0CAC-48FF-8068-DFD62AF03E54}"/>
@@ -2490,36 +2490,36 @@
     <hyperlink ref="A3" r:id="rId27" xr:uid="{89BFC874-8B1C-4D17-B994-2B65C747E8C0}"/>
     <hyperlink ref="A6" r:id="rId28" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Alexandre_Falgui%C3%A8re_-_Vainqueur_au_combat_de_coqs_%281864%29.jpg/1280px-Alexandre_Falgui%C3%A8re_-_Vainqueur_au_combat_de_coqs_%281864%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{66400BC1-750E-4E87-8FBE-FD7F73FC6627}"/>
     <hyperlink ref="A13" r:id="rId29" xr:uid="{9B504E9C-BEFD-44B3-B869-73F9586CB5DD}"/>
-    <hyperlink ref="A20" r:id="rId30" xr:uid="{F96C6218-3DC6-429C-B97C-87BF1E56849A}"/>
-    <hyperlink ref="A21" r:id="rId31" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7d/%D0%92%D0%B0%D1%80%D1%88%D0%B0%D0%B2%D0%B0_-_panoramio_%28130%29.jpg/960px-%D0%92%D0%B0%D1%80%D1%88%D0%B0%D0%B2%D0%B0_-_panoramio_%28130%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C8A305DF-A6C9-495D-A1AE-772305FE8261}"/>
-    <hyperlink ref="A26" r:id="rId32" xr:uid="{2F6A5E41-3E4A-4779-A7AC-6E7CCB64D22F}"/>
-    <hyperlink ref="A28" r:id="rId33" xr:uid="{69ED9E12-C396-431B-B8F1-F28D0A602E98}"/>
-    <hyperlink ref="A31" r:id="rId34" xr:uid="{5D77A0CA-8CD6-4D49-A28D-511CDA7EB67C}"/>
-    <hyperlink ref="A33" r:id="rId35" xr:uid="{514B81EE-8CFE-4D60-B5B0-5356CB9EA31C}"/>
-    <hyperlink ref="A34" r:id="rId36" xr:uid="{23FD7F71-63B7-4AB4-8686-0324907807CC}"/>
-    <hyperlink ref="A44" r:id="rId37" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/82/Estatua_de_Miguel_de_Cervantes_%286_de_diciembre_de_2005%2C_Madrid%29_02.JPG/960px-Estatua_de_Miguel_de_Cervantes_%286_de_diciembre_de_2005%2C_Madrid%29_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3C5133CF-9130-42BB-A7D6-CB138529FEF1}"/>
-    <hyperlink ref="A49" r:id="rId38" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Museo_Nacional_de_Arte_Mexico_DF%2C_Manuel_Vilarm_Tlahuicole_General_Tlaxcalteca_1851_%2822153403811%29.jpg/960px-Museo_Nacional_de_Arte_Mexico_DF%2C_Manuel_Vilarm_Tlahuicole_General_Tlaxcalteca_1851_%2822153403811%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{79E9BD51-D020-4923-B07B-A9E25539D93B}"/>
-    <hyperlink ref="A51" r:id="rId39" xr:uid="{A7D3B521-73D8-4D12-859C-2BDA5FC5C9BD}"/>
-    <hyperlink ref="A52" r:id="rId40" xr:uid="{CA64DF7E-88F5-4722-9B9E-3997A75ED0E6}"/>
-    <hyperlink ref="A55" r:id="rId41" xr:uid="{8D8DDFC6-5BF8-4844-8322-7EA28FA6DABB}"/>
-    <hyperlink ref="A56" r:id="rId42" xr:uid="{6064E09D-244B-4911-A11E-B70667B83E98}"/>
-    <hyperlink ref="A57" r:id="rId43" xr:uid="{AAF4E702-D56A-42D5-B8AC-681CCB9FEA8B}"/>
-    <hyperlink ref="A58" r:id="rId44" xr:uid="{4D5F0FFE-B7F1-44B3-AF08-F23CBE027110}"/>
-    <hyperlink ref="A60" r:id="rId45" xr:uid="{5B30924F-F0D1-4E32-AB4E-55BA8203119E}"/>
-    <hyperlink ref="A61" r:id="rId46" xr:uid="{C3FEF373-80EC-4A05-90A7-AEB83324E5A6}"/>
-    <hyperlink ref="A5" r:id="rId47" xr:uid="{A48CCD89-6B56-4EFB-8B6C-0A0ECFB8F8D9}"/>
-    <hyperlink ref="A10" r:id="rId48" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{E0F148C3-98D3-4E2A-8358-EC141CC2F650}"/>
-    <hyperlink ref="A12" r:id="rId49" xr:uid="{FDCF47B0-83FC-43BA-AB5E-5BC09158CB1B}"/>
-    <hyperlink ref="A2" r:id="rId50" xr:uid="{D9C63A8D-77EF-4A24-B9AE-8F969F98DF09}"/>
-    <hyperlink ref="A23" r:id="rId51" xr:uid="{71A67ADA-0476-4DFA-936A-C01BA1530CFD}"/>
-    <hyperlink ref="A39" r:id="rId52" xr:uid="{AE678BD0-0675-4E63-AE8B-3C4F5ECC09A8}"/>
-    <hyperlink ref="A4" r:id="rId53" xr:uid="{2A739E13-8E3D-4F75-98E1-B2F4CF151CE6}"/>
-    <hyperlink ref="A7" r:id="rId54" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Au_But_%28Alfred_Boucher%29_01.jpg/1280px-Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Au_But_%28Alfred_Boucher%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{C2C06555-D109-465D-866A-4425B3188ADF}"/>
-    <hyperlink ref="A30" r:id="rId55" xr:uid="{B4AB73FA-E9A5-492E-8460-0035A08F308A}"/>
-    <hyperlink ref="A35" r:id="rId56" xr:uid="{F973385B-28E1-4561-B45F-9E74717E7F46}"/>
-    <hyperlink ref="A48" r:id="rId57" xr:uid="{25939432-0835-4ADE-B2CC-A35A5B80D956}"/>
-    <hyperlink ref="A32" r:id="rId58" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/55/Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg/960px-Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2F91C6EB-DC08-4036-AA37-7146C9AE0D12}"/>
-    <hyperlink ref="A18" r:id="rId59" xr:uid="{28AA9905-A101-4E4D-B41B-763B78D611CD}"/>
+    <hyperlink ref="A21" r:id="rId30" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/7d/%D0%92%D0%B0%D1%80%D1%88%D0%B0%D0%B2%D0%B0_-_panoramio_%28130%29.jpg/960px-%D0%92%D0%B0%D1%80%D1%88%D0%B0%D0%B2%D0%B0_-_panoramio_%28130%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C8A305DF-A6C9-495D-A1AE-772305FE8261}"/>
+    <hyperlink ref="A27" r:id="rId31" xr:uid="{2F6A5E41-3E4A-4779-A7AC-6E7CCB64D22F}"/>
+    <hyperlink ref="A29" r:id="rId32" xr:uid="{69ED9E12-C396-431B-B8F1-F28D0A602E98}"/>
+    <hyperlink ref="A33" r:id="rId33" xr:uid="{514B81EE-8CFE-4D60-B5B0-5356CB9EA31C}"/>
+    <hyperlink ref="A34" r:id="rId34" xr:uid="{23FD7F71-63B7-4AB4-8686-0324907807CC}"/>
+    <hyperlink ref="A44" r:id="rId35" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/82/Estatua_de_Miguel_de_Cervantes_%286_de_diciembre_de_2005%2C_Madrid%29_02.JPG/960px-Estatua_de_Miguel_de_Cervantes_%286_de_diciembre_de_2005%2C_Madrid%29_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3C5133CF-9130-42BB-A7D6-CB138529FEF1}"/>
+    <hyperlink ref="A49" r:id="rId36" display="https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Museo_Nacional_de_Arte_Mexico_DF%2C_Manuel_Vilarm_Tlahuicole_General_Tlaxcalteca_1851_%2822153403811%29.jpg/960px-Museo_Nacional_de_Arte_Mexico_DF%2C_Manuel_Vilarm_Tlahuicole_General_Tlaxcalteca_1851_%2822153403811%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{79E9BD51-D020-4923-B07B-A9E25539D93B}"/>
+    <hyperlink ref="A51" r:id="rId37" xr:uid="{A7D3B521-73D8-4D12-859C-2BDA5FC5C9BD}"/>
+    <hyperlink ref="A52" r:id="rId38" xr:uid="{CA64DF7E-88F5-4722-9B9E-3997A75ED0E6}"/>
+    <hyperlink ref="A55" r:id="rId39" xr:uid="{8D8DDFC6-5BF8-4844-8322-7EA28FA6DABB}"/>
+    <hyperlink ref="A56" r:id="rId40" xr:uid="{6064E09D-244B-4911-A11E-B70667B83E98}"/>
+    <hyperlink ref="A57" r:id="rId41" xr:uid="{AAF4E702-D56A-42D5-B8AC-681CCB9FEA8B}"/>
+    <hyperlink ref="A58" r:id="rId42" xr:uid="{4D5F0FFE-B7F1-44B3-AF08-F23CBE027110}"/>
+    <hyperlink ref="A60" r:id="rId43" xr:uid="{5B30924F-F0D1-4E32-AB4E-55BA8203119E}"/>
+    <hyperlink ref="A61" r:id="rId44" xr:uid="{C3FEF373-80EC-4A05-90A7-AEB83324E5A6}"/>
+    <hyperlink ref="A5" r:id="rId45" xr:uid="{A48CCD89-6B56-4EFB-8B6C-0A0ECFB8F8D9}"/>
+    <hyperlink ref="A10" r:id="rId46" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{E0F148C3-98D3-4E2A-8358-EC141CC2F650}"/>
+    <hyperlink ref="A12" r:id="rId47" xr:uid="{FDCF47B0-83FC-43BA-AB5E-5BC09158CB1B}"/>
+    <hyperlink ref="A2" r:id="rId48" xr:uid="{D9C63A8D-77EF-4A24-B9AE-8F969F98DF09}"/>
+    <hyperlink ref="A23" r:id="rId49" xr:uid="{71A67ADA-0476-4DFA-936A-C01BA1530CFD}"/>
+    <hyperlink ref="A39" r:id="rId50" xr:uid="{AE678BD0-0675-4E63-AE8B-3C4F5ECC09A8}"/>
+    <hyperlink ref="A4" r:id="rId51" xr:uid="{2A739E13-8E3D-4F75-98E1-B2F4CF151CE6}"/>
+    <hyperlink ref="A7" r:id="rId52" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Au_But_%28Alfred_Boucher%29_01.jpg/1280px-Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Au_But_%28Alfred_Boucher%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{C2C06555-D109-465D-866A-4425B3188ADF}"/>
+    <hyperlink ref="A31" r:id="rId53" xr:uid="{B4AB73FA-E9A5-492E-8460-0035A08F308A}"/>
+    <hyperlink ref="A35" r:id="rId54" xr:uid="{F973385B-28E1-4561-B45F-9E74717E7F46}"/>
+    <hyperlink ref="A48" r:id="rId55" xr:uid="{25939432-0835-4ADE-B2CC-A35A5B80D956}"/>
+    <hyperlink ref="A32" r:id="rId56" display="https://upload.wikimedia.org/wikipedia/commons/thumb/5/55/Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg/960px-Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2F91C6EB-DC08-4036-AA37-7146C9AE0D12}"/>
+    <hyperlink ref="A18" r:id="rId57" xr:uid="{28AA9905-A101-4E4D-B41B-763B78D611CD}"/>
+    <hyperlink ref="A20" r:id="rId58" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f6/Belgique_-_Bruxelles_-_Botanique_-_L%27Automne_ou_Le_Semeur_de_Constantin_Meunier_-_01.jpg/960px-Belgique_-_Bruxelles_-_Botanique_-_L%27Automne_ou_Le_Semeur_de_Constantin_Meunier_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AE006778-7DEC-44E3-82F2-A553E9283371}"/>
+    <hyperlink ref="A26" r:id="rId59" xr:uid="{3A92963C-09BA-4F43-B04C-FA44097AAC8F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
